--- a/ZonasEscolares/excels/PIURA-PIURA-VEINTISEIS_DE_OCTUBRE.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-VEINTISEIS_DE_OCTUBRE.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VEINTISEIS_DE_OCTUBRE</t>
+          <t>VEINTISEIS DE OCTUBRE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PIURA-PIURA-VEINTISEIS_DE_OCTUBRE.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-VEINTISEIS_DE_OCTUBRE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>004 GUILLERMO GULMAN LAPOUBLE</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-5.19359</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-80.64465</v>
-      </c>
-      <c r="I2" t="n">
-        <v>250</v>
-      </c>
-      <c r="J2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-5.19359</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-80.64465</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>018 DOMINGO SAVIO</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-5.18592</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-80.66399</v>
-      </c>
-      <c r="I3" t="n">
-        <v>274</v>
-      </c>
-      <c r="J3" t="n">
-        <v>12</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-5.18592</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-80.66399</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>021</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-5.18902</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-80.65509</v>
-      </c>
-      <c r="I4" t="n">
-        <v>277</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-5.18902</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-80.65509</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>SAN JOSE</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-5.1922</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-80.64585</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1361</v>
-      </c>
-      <c r="J5" t="n">
-        <v>49</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-5.1922</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-80.64585</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>14005 LUCIA ESTELA ECHEANDIA ALTUNA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-5.1953</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-80.6429</v>
-      </c>
-      <c r="I6" t="n">
-        <v>450</v>
-      </c>
-      <c r="J6" t="n">
-        <v>21</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-5.1953</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-80.6429</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>14008 LEONOR CERNA DE VALDIVIEZO</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-5.18553</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-80.6636</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1195</v>
-      </c>
-      <c r="J7" t="n">
-        <v>54</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-5.18553</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-80.6636</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1195</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>14011 NUESTRA SEÑORA DEL PILAR</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-5.184591</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-80.667862</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1893</v>
-      </c>
-      <c r="J8" t="n">
-        <v>87</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-5.184591</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-80.667862</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>14012 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-5.184</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-80.6737</v>
-      </c>
-      <c r="I9" t="n">
-        <v>760</v>
-      </c>
-      <c r="J9" t="n">
-        <v>34</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-5.184</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-80.6737</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>SEÑOR DE LA DIVINA MISERICORDIA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-5.19179</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-80.66309</v>
-      </c>
-      <c r="I10" t="n">
-        <v>562</v>
-      </c>
-      <c r="J10" t="n">
-        <v>21</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-5.19179</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-80.66309</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>14015 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-5.19284</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-80.6584</v>
-      </c>
-      <c r="I11" t="n">
-        <v>627</v>
-      </c>
-      <c r="J11" t="n">
-        <v>26</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-5.19284</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-80.6584</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>15110 JOSE GABRIEL CONDORCANQUI</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-5.1957</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-80.6561</v>
-      </c>
-      <c r="I12" t="n">
-        <v>700</v>
-      </c>
-      <c r="J12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-5.1957</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-80.6561</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>15177 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-5.18998</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-80.67147</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1487</v>
-      </c>
-      <c r="J13" t="n">
-        <v>67</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-5.18998</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-80.67147</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1487</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>15282</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-5.1945</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-80.65349999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>341</v>
-      </c>
-      <c r="J14" t="n">
-        <v>15</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-5.1945</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-80.6535</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>15317 CESAR ABRAHAM VALLEJO MENDOZA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-5.1972</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-80.6452</v>
-      </c>
-      <c r="I15" t="n">
-        <v>462</v>
-      </c>
-      <c r="J15" t="n">
-        <v>19</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-5.1972</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-80.6452</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>MICAELA BASTIDAS</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-5.17931</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-80.67433</v>
-      </c>
-      <c r="I16" t="n">
-        <v>929</v>
-      </c>
-      <c r="J16" t="n">
-        <v>41</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-5.17931</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-80.67433</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>20015 SAN SEBASTIAN</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-5.18271</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-80.68011</v>
-      </c>
-      <c r="I17" t="n">
-        <v>472</v>
-      </c>
-      <c r="J17" t="n">
-        <v>20</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-5.18271</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-80.68011</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>20138</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-5.1747</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-80.6846</v>
-      </c>
-      <c r="I18" t="n">
-        <v>839</v>
-      </c>
-      <c r="J18" t="n">
-        <v>29</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-5.1747</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-80.6846</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>LUIS ALBERTO SANCHEZ SANCHEZ</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-5.18706</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-80.65774</v>
-      </c>
-      <c r="I19" t="n">
-        <v>868</v>
-      </c>
-      <c r="J19" t="n">
-        <v>45</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-5.18706</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-80.65774</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-5.19724</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-80.661215</v>
-      </c>
-      <c r="I20" t="n">
-        <v>903</v>
-      </c>
-      <c r="J20" t="n">
-        <v>35</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-5.19724</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-80.661215</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>JORGE BASADRE</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-5.184571</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-80.6617</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2083</v>
-      </c>
-      <c r="J21" t="n">
-        <v>97</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-5.184571</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-80.6617</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2083</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-5.18211</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-80.67198</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1130</v>
-      </c>
-      <c r="J22" t="n">
-        <v>63</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-5.18211</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-80.67198</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-5.18907</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-80.66316</v>
-      </c>
-      <c r="I23" t="n">
-        <v>646</v>
-      </c>
-      <c r="J23" t="n">
-        <v>41</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-5.18907</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-80.66316</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>SAN JOSE OBRERO</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-5.19233</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-80.64358</v>
-      </c>
-      <c r="I24" t="n">
-        <v>710</v>
-      </c>
-      <c r="J24" t="n">
-        <v>42</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-5.19233</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-80.64358</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>JUAN JACOBO ROUSSEAU</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-5.198661</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-80.64391999999999</v>
-      </c>
-      <c r="I25" t="n">
-        <v>366</v>
-      </c>
-      <c r="J25" t="n">
-        <v>22</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-5.198661</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-80.64392</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-5.18363</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-80.66845000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>744</v>
-      </c>
-      <c r="J26" t="n">
-        <v>35</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-5.18363</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-80.66845</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-5.18741</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-80.66171</v>
-      </c>
-      <c r="I27" t="n">
-        <v>736</v>
-      </c>
-      <c r="J27" t="n">
-        <v>36</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-5.18741</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-80.66171</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>FE Y ALEGRIA 49</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-5.18236</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-80.68428</v>
-      </c>
-      <c r="I28" t="n">
-        <v>716</v>
-      </c>
-      <c r="J28" t="n">
-        <v>38</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-5.18236</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-80.68428</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>CENTRO DE APLICACION UCV COLLEGE</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-5.1759</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-80.66248</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1173</v>
-      </c>
-      <c r="J29" t="n">
-        <v>94</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-5.1759</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-80.66248</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1173</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>ISACC NEWTON</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-5.18528</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-80.66638</v>
-      </c>
-      <c r="I30" t="n">
-        <v>286</v>
-      </c>
-      <c r="J30" t="n">
-        <v>8</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-5.18528</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-80.66638</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>SANTA SOFIA</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-5.19951</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-80.64664</v>
-      </c>
-      <c r="I31" t="n">
-        <v>293</v>
-      </c>
-      <c r="J31" t="n">
-        <v>18</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-5.19951</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-80.64664</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>JESUS MARIA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-5.160421</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-80.664282</v>
-      </c>
-      <c r="I32" t="n">
-        <v>367</v>
-      </c>
-      <c r="J32" t="n">
-        <v>17</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-5.160421</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-80.664282</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-5.17387</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-80.68767</v>
-      </c>
-      <c r="I33" t="n">
-        <v>491</v>
-      </c>
-      <c r="J33" t="n">
-        <v>24</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-5.17387</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-80.68767</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>PRINCIPE DE PAZ</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-5.20438</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-80.65012</v>
-      </c>
-      <c r="I34" t="n">
-        <v>284</v>
-      </c>
-      <c r="J34" t="n">
-        <v>16</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-5.20438</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-80.65012</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>1333</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-5.189421</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-80.677251</v>
-      </c>
-      <c r="I35" t="n">
-        <v>47</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-5.189421</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-80.677251</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>20463 MONSEÑOR RAMON ZUBIETA</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-5.16464</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-80.6537</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1012</v>
-      </c>
-      <c r="J36" t="n">
-        <v>46</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-5.16464</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-80.6537</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>1392</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-5.180589</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-80.672419</v>
-      </c>
-      <c r="I37" t="n">
-        <v>234</v>
-      </c>
-      <c r="J37" t="n">
-        <v>9</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-5.180589</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-80.672419</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>FUTURA SCHOOLS</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-5.17287</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-80.66549000000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>729</v>
-      </c>
-      <c r="J38" t="n">
-        <v>30</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-5.17287</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-80.66549</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>1546</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-5.190019</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-80.667243</v>
-      </c>
-      <c r="I39" t="n">
-        <v>15</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-5.190019</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-80.667243</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>DIOS ES AMOR</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-5.15778</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-80.67033000000001</v>
-      </c>
-      <c r="I40" t="n">
-        <v>319</v>
-      </c>
-      <c r="J40" t="n">
-        <v>15</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-5.15778</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-80.67033</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>LEON TEMPUS</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-5.17639</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-80.69289000000001</v>
-      </c>
-      <c r="I41" t="n">
-        <v>210</v>
-      </c>
-      <c r="J41" t="n">
-        <v>13</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-5.17639</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-80.69289</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/PIURA-PIURA-VEINTISEIS_DE_OCTUBRE.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-VEINTISEIS_DE_OCTUBRE.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>409961</t>
+          <t>820551</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>004 GUILLERMO GULMAN LAPOUBLE</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.19359</t>
+          <t>-5.190019</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-80.64465</t>
+          <t>-80.667243</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>410016</t>
+          <t>409961</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>018 DOMINGO SAVIO</t>
+          <t>004 GUILLERMO GULMAN LAPOUBLE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.18592</t>
+          <t>-5.19359</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-80.66399</t>
+          <t>-80.64465</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,27 +625,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>410040</t>
+          <t>410016</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>018 DOMINGO SAVIO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.18902</t>
+          <t>-5.18592</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-80.65509</t>
+          <t>-80.66399</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>410295</t>
+          <t>410040</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SAN JOSE</t>
+          <t>021</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.1922</t>
+          <t>-5.18902</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-80.64585</t>
+          <t>-80.65509</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>277</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>410304</t>
+          <t>829660</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14005 LUCIA ESTELA ECHEANDIA ALTUNA</t>
+          <t>LEON TEMPUS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.1953</t>
+          <t>-5.17639</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-80.6429</t>
+          <t>-80.69289</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>410323</t>
+          <t>410498</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14008 LEONOR CERNA DE VALDIVIEZO</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.18553</t>
+          <t>-5.1945</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-80.6636</t>
+          <t>-80.6535</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>341</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>410337</t>
+          <t>829448</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14011 NUESTRA SEÑORA DEL PILAR</t>
+          <t>DIOS ES AMOR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.184591</t>
+          <t>-5.15778</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-80.667862</t>
+          <t>-80.67033</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>319</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>410342</t>
+          <t>656211</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14012 SAN MARTIN DE PORRES</t>
+          <t>PRINCIPE DE PAZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.184</t>
+          <t>-5.20438</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-80.6737</t>
+          <t>-80.65012</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>284</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>410356</t>
+          <t>632381</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA DIVINA MISERICORDIA</t>
+          <t>JESUS MARIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.19179</t>
+          <t>-5.160421</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-80.66309</t>
+          <t>-80.664282</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>367</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>410361</t>
+          <t>533866</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14015 NUESTRA SEÑORA DEL CARMEN</t>
+          <t>SANTA SOFIA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.19284</t>
+          <t>-5.19951</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-80.6584</t>
+          <t>-80.64664</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>293</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>410455</t>
+          <t>410506</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>15110 JOSE GABRIEL CONDORCANQUI</t>
+          <t>15317 CESAR ABRAHAM VALLEJO MENDOZA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.1957</t>
+          <t>-5.1972</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-80.6561</t>
+          <t>-80.6452</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>462</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>410460</t>
+          <t>765564</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15177 JOSE OLAYA BALANDRA</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.18998</t>
+          <t>-5.189421</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-80.67147</t>
+          <t>-80.677251</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>410498</t>
+          <t>410530</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>20015 SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.1945</t>
+          <t>-5.18271</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-80.6535</t>
+          <t>-80.68011</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>472</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>410506</t>
+          <t>410304</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15317 CESAR ABRAHAM VALLEJO MENDOZA</t>
+          <t>14005 LUCIA ESTELA ECHEANDIA ALTUNA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.1972</t>
+          <t>-5.1953</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-80.6452</t>
+          <t>-80.6429</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>450</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>410511</t>
+          <t>410356</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MICAELA BASTIDAS</t>
+          <t>SEÑOR DE LA DIVINA MISERICORDIA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.17931</t>
+          <t>-5.19179</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-80.67433</t>
+          <t>-80.66309</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>562</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>410530</t>
+          <t>411563</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20015 SAN SEBASTIAN</t>
+          <t>JUAN JACOBO ROUSSEAU</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.18271</t>
+          <t>-5.198661</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-80.68011</t>
+          <t>-80.64392</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>366</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>410592</t>
+          <t>656193</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.1747</t>
+          <t>-5.17387</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-80.6846</t>
+          <t>-80.68767</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>491</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>410686</t>
+          <t>410361</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO SANCHEZ SANCHEZ</t>
+          <t>14015 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.18706</t>
+          <t>-5.19284</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-80.65774</t>
+          <t>-80.6584</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>627</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>410714</t>
+          <t>410455</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ALMIRANTE MIGUEL GRAU</t>
+          <t>15110 JOSE GABRIEL CONDORCANQUI</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.19724</t>
+          <t>-5.1957</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-80.661215</t>
+          <t>-80.6561</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>700</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>410747</t>
+          <t>410592</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JORGE BASADRE</t>
+          <t>20138</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.184571</t>
+          <t>-5.1747</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-80.6617</t>
+          <t>-80.6846</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>839</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>410766</t>
+          <t>806574</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA</t>
+          <t>FUTURA SCHOOLS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.18211</t>
+          <t>-5.17287</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-80.67198</t>
+          <t>-80.66549</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>729</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>410832</t>
+          <t>410342</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
+          <t>14012 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.18907</t>
+          <t>-5.184</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-80.66316</t>
+          <t>-80.6737</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>760</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>411308</t>
+          <t>410714</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SAN JOSE OBRERO</t>
+          <t>ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.19233</t>
+          <t>-5.19724</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-80.64358</t>
+          <t>-80.661215</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>903</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>411563</t>
+          <t>411600</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JUAN JACOBO ROUSSEAU</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.198661</t>
+          <t>-5.18363</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-80.64392</t>
+          <t>-80.66845</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>744</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>411600</t>
+          <t>411619</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.18363</t>
+          <t>-5.18741</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-80.66845</t>
+          <t>-80.66171</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>736</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>411619</t>
+          <t>412138</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>FE Y ALEGRIA 49</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.18741</t>
+          <t>-5.18236</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-80.66171</t>
+          <t>-80.68428</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>716</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>412138</t>
+          <t>410511</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 49</t>
+          <t>MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.18236</t>
+          <t>-5.17931</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-80.68428</t>
+          <t>-80.67433</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>929</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>509084</t>
+          <t>410832</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CENTRO DE APLICACION UCV COLLEGE</t>
+          <t>NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.1759</t>
+          <t>-5.18907</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-80.66248</t>
+          <t>-80.66316</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>646</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>517178</t>
+          <t>411308</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ISACC NEWTON</t>
+          <t>SAN JOSE OBRERO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.18528</t>
+          <t>-5.19233</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-80.66638</t>
+          <t>-80.64358</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>710</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>533866</t>
+          <t>410686</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SANTA SOFIA</t>
+          <t>LUIS ALBERTO SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.19951</t>
+          <t>-5.18706</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-80.64664</t>
+          <t>-80.65774</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>868</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>632381</t>
+          <t>766083</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JESUS MARIA</t>
+          <t>20463 MONSEÑOR RAMON ZUBIETA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-5.160421</t>
+          <t>-5.16464</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-80.664282</t>
+          <t>-80.6537</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>656193</t>
+          <t>410295</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO JESUS</t>
+          <t>SAN JOSE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.17387</t>
+          <t>-5.1922</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-80.68767</t>
+          <t>-80.64585</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>656211</t>
+          <t>410323</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PRINCIPE DE PAZ</t>
+          <t>14008 LEONOR CERNA DE VALDIVIEZO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.20438</t>
+          <t>-5.18553</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-80.65012</t>
+          <t>-80.6636</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,37 +2547,37 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>765564</t>
+          <t>410766</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.189421</t>
+          <t>-5.18211</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-80.677251</t>
+          <t>-80.67198</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>766083</t>
+          <t>410460</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20463 MONSEÑOR RAMON ZUBIETA</t>
+          <t>15177 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5.16464</t>
+          <t>-5.18998</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-80.6537</t>
+          <t>-80.67147</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>796438</t>
+          <t>517178</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>ISACC NEWTON</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.180589</t>
+          <t>-5.18528</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-80.672419</t>
+          <t>-80.66638</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>286</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>806574</t>
+          <t>410337</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FUTURA SCHOOLS</t>
+          <t>14011 NUESTRA SEÑORA DEL PILAR</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.17287</t>
+          <t>-5.184591</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-80.66549</t>
+          <t>-80.667862</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,37 +2795,37 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>820551</t>
+          <t>796438</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5.190019</t>
+          <t>-5.180589</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-80.667243</t>
+          <t>-80.672419</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2857,37 +2857,37 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>829448</t>
+          <t>509084</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>DIOS ES AMOR</t>
+          <t>CENTRO DE APLICACION UCV COLLEGE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5.15778</t>
+          <t>-5.1759</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-80.67033</t>
+          <t>-80.66248</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>829660</t>
+          <t>410747</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LEON TEMPUS</t>
+          <t>JORGE BASADRE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-5.17639</t>
+          <t>-5.184571</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-80.69289</t>
+          <t>-80.6617</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">

--- a/ZonasEscolares/excels/PIURA-PIURA-VEINTISEIS_DE_OCTUBRE.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-VEINTISEIS_DE_OCTUBRE.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>820551</t>
+          <t>829660</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>LEON TEMPUS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.190019</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-80.667243</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-5.17639</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-80.69289</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>409961</t>
+          <t>829448</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>004 GUILLERMO GULMAN LAPOUBLE</t>
+          <t>DIOS ES AMOR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.19359</t>
+          <t>319</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-80.64465</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>-5.15778</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-80.67033</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>410016</t>
+          <t>820551</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>018 DOMINGO SAVIO</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.18592</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-80.66399</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-5.190019</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-80.667243</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>410040</t>
+          <t>806574</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>FUTURA SCHOOLS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.18902</t>
+          <t>729</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-80.65509</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>-5.17287</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-80.66549</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>829660</t>
+          <t>796438</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LEON TEMPUS</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.17639</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-80.69289</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-5.180589</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-80.672419</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>410498</t>
+          <t>766083</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>20463 MONSEÑOR RAMON ZUBIETA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.1945</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-80.6535</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>-5.16464</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-80.6537</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>829448</t>
+          <t>765564</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DIOS ES AMOR</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.15778</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-80.67033</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>-5.189421</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-80.677251</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -945,22 +945,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>-5.20438</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>-80.65012</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>632381</t>
+          <t>656193</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JESUS MARIA</t>
+          <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.160421</t>
+          <t>491</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-80.664282</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>-5.17387</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-80.68767</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>533866</t>
+          <t>632381</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SANTA SOFIA</t>
+          <t>JESUS MARIA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.19951</t>
+          <t>367</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-80.64664</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>-5.160421</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-80.664282</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>410506</t>
+          <t>533866</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>15317 CESAR ABRAHAM VALLEJO MENDOZA</t>
+          <t>SANTA SOFIA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.1972</t>
+          <t>293</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-80.6452</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>-5.19951</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-80.64664</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>765564</t>
+          <t>517178</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>ISACC NEWTON</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.189421</t>
+          <t>286</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-80.677251</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-5.18528</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-80.66638</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>410530</t>
+          <t>509084</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20015 SAN SEBASTIAN</t>
+          <t>CENTRO DE APLICACION UCV COLLEGE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.18271</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-80.68011</t>
+          <t>94</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>-5.1759</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-80.66248</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>410304</t>
+          <t>412138</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>14005 LUCIA ESTELA ECHEANDIA ALTUNA</t>
+          <t>FE Y ALEGRIA 49</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.1953</t>
+          <t>716</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-80.6429</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>-5.18236</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-80.68428</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>410356</t>
+          <t>411619</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA DIVINA MISERICORDIA</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.19179</t>
+          <t>736</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-80.66309</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>-5.18741</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-80.66171</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>411563</t>
+          <t>411600</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JUAN JACOBO ROUSSEAU</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.198661</t>
+          <t>744</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-80.64392</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>-5.18363</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-80.66845</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>656193</t>
+          <t>411563</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO JESUS</t>
+          <t>JUAN JACOBO ROUSSEAU</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.17387</t>
+          <t>366</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-80.68767</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>-5.198661</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-80.64392</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>410361</t>
+          <t>411308</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14015 NUESTRA SEÑORA DEL CARMEN</t>
+          <t>SAN JOSE OBRERO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.19284</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-80.6584</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>-5.19233</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-80.64358</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>410455</t>
+          <t>410832</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15110 JOSE GABRIEL CONDORCANQUI</t>
+          <t>NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.1957</t>
+          <t>646</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-80.6561</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>-5.18907</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-80.66316</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>410592</t>
+          <t>410766</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.1747</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-80.6846</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>-5.18211</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-80.67198</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>806574</t>
+          <t>410747</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FUTURA SCHOOLS</t>
+          <t>JORGE BASADRE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.17287</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-80.66549</t>
+          <t>97</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>-5.184571</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-80.6617</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>410342</t>
+          <t>410714</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14012 SAN MARTIN DE PORRES</t>
+          <t>ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.184</t>
+          <t>903</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-80.6737</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>-5.19724</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-80.661215</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>410714</t>
+          <t>410686</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ALMIRANTE MIGUEL GRAU</t>
+          <t>LUIS ALBERTO SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.19724</t>
+          <t>868</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-80.661215</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>-5.18706</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-80.65774</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>411600</t>
+          <t>410592</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>20138</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.18363</t>
+          <t>839</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-80.66845</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>-5.1747</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-80.6846</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>411619</t>
+          <t>410530</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>20015 SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.18741</t>
+          <t>472</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-80.66171</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>-5.18271</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-80.68011</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>412138</t>
+          <t>410511</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 49</t>
+          <t>MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.18236</t>
+          <t>929</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-80.68428</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>-5.17931</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-80.67433</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>410511</t>
+          <t>410506</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MICAELA BASTIDAS</t>
+          <t>15317 CESAR ABRAHAM VALLEJO MENDOZA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.17931</t>
+          <t>462</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-80.67433</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>-5.1972</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-80.6452</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>410832</t>
+          <t>410498</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.18907</t>
+          <t>341</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-80.66316</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>-5.1945</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-80.6535</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>411308</t>
+          <t>410460</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SAN JOSE OBRERO</t>
+          <t>15177 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.19233</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-80.64358</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>-5.18998</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-80.67147</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>410686</t>
+          <t>410455</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO SANCHEZ SANCHEZ</t>
+          <t>15110 JOSE GABRIEL CONDORCANQUI</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.18706</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-80.65774</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>-5.1957</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-80.6561</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>766083</t>
+          <t>410361</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20463 MONSEÑOR RAMON ZUBIETA</t>
+          <t>14015 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-5.16464</t>
+          <t>627</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-80.6537</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>-5.19284</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-80.6584</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>410295</t>
+          <t>410356</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SAN JOSE</t>
+          <t>SEÑOR DE LA DIVINA MISERICORDIA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.1922</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-80.64585</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>-5.19179</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-80.66309</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>410323</t>
+          <t>410342</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>14008 LEONOR CERNA DE VALDIVIEZO</t>
+          <t>14012 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.18553</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-80.6636</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>-5.184</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-80.6737</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>410766</t>
+          <t>410337</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA</t>
+          <t>14011 NUESTRA SEÑORA DEL PILAR</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.18211</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-80.67198</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>-5.184591</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-80.667862</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>410460</t>
+          <t>410323</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>15177 JOSE OLAYA BALANDRA</t>
+          <t>14008 LEONOR CERNA DE VALDIVIEZO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5.18998</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-80.67147</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>-5.18553</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-80.6636</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>517178</t>
+          <t>410304</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ISACC NEWTON</t>
+          <t>14005 LUCIA ESTELA ECHEANDIA ALTUNA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.18528</t>
+          <t>450</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-80.66638</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>-5.1953</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-80.6429</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>410337</t>
+          <t>410295</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>14011 NUESTRA SEÑORA DEL PILAR</t>
+          <t>SAN JOSE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.184591</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-80.667862</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>-5.1922</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>-80.64585</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>796438</t>
+          <t>410040</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>021</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5.180589</t>
+          <t>277</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-80.672419</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-5.18902</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-80.65509</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,37 +2857,37 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>509084</t>
+          <t>410016</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CENTRO DE APLICACION UCV COLLEGE</t>
+          <t>018 DOMINGO SAVIO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5.1759</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-80.66248</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>-5.18592</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>-80.66399</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>410747</t>
+          <t>409961</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>JORGE BASADRE</t>
+          <t>004 GUILLERMO GULMAN LAPOUBLE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-5.184571</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-80.6617</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>-5.19359</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-80.64465</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">

--- a/ZonasEscolares/excels/PIURA-PIURA-VEINTISEIS_DE_OCTUBRE.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-VEINTISEIS_DE_OCTUBRE.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
